--- a/examples/data/example_2_one_sheet_per_trial.xlsx
+++ b/examples/data/example_2_one_sheet_per_trial.xlsx
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>Date 1</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>Date 1</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>Date 1</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>Date 1</t>
         </is>
       </c>
     </row>

--- a/examples/data/example_2_one_sheet_per_trial.xlsx
+++ b/examples/data/example_2_one_sheet_per_trial.xlsx
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -1180,7 +1180,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -1188,7 +1188,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -1196,7 +1196,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -1212,7 +1212,7 @@
         <v>6</v>
       </c>
       <c r="B13" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -1220,7 +1220,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -1228,7 +1228,7 @@
         <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
@@ -1236,7 +1236,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -1244,7 +1244,7 @@
         <v>10</v>
       </c>
       <c r="B17" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -1252,7 +1252,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
@@ -1260,7 +1260,7 @@
         <v>12</v>
       </c>
       <c r="B19" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -1268,7 +1268,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -1276,7 +1276,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -1284,7 +1284,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -1292,7 +1292,7 @@
         <v>16</v>
       </c>
       <c r="B23" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
@@ -1300,7 +1300,7 @@
         <v>17</v>
       </c>
       <c r="B24" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
@@ -1308,7 +1308,7 @@
         <v>18</v>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
@@ -1316,7 +1316,7 @@
         <v>19</v>
       </c>
       <c r="B26" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27">
@@ -1324,7 +1324,7 @@
         <v>20</v>
       </c>
       <c r="B27" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
@@ -1332,7 +1332,7 @@
         <v>21</v>
       </c>
       <c r="B28" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
@@ -1340,7 +1340,7 @@
         <v>22</v>
       </c>
       <c r="B29" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
@@ -1348,7 +1348,7 @@
         <v>23</v>
       </c>
       <c r="B30" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
@@ -1356,7 +1356,7 @@
         <v>24</v>
       </c>
       <c r="B31" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32">
@@ -1372,7 +1372,7 @@
         <v>26</v>
       </c>
       <c r="B33" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
@@ -1380,7 +1380,7 @@
         <v>27</v>
       </c>
       <c r="B34" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35">
@@ -1388,7 +1388,7 @@
         <v>28</v>
       </c>
       <c r="B35" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36">
@@ -1396,7 +1396,7 @@
         <v>29</v>
       </c>
       <c r="B36" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37">
@@ -1404,7 +1404,7 @@
         <v>30</v>
       </c>
       <c r="B37" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
@@ -1412,7 +1412,7 @@
         <v>31</v>
       </c>
       <c r="B38" t="n">
-        <v>50</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39">
@@ -1420,7 +1420,7 @@
         <v>32</v>
       </c>
       <c r="B39" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
@@ -1428,7 +1428,7 @@
         <v>33</v>
       </c>
       <c r="B40" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41">
@@ -1436,7 +1436,7 @@
         <v>34</v>
       </c>
       <c r="B41" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42">
@@ -1444,7 +1444,7 @@
         <v>35</v>
       </c>
       <c r="B42" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
@@ -1452,7 +1452,7 @@
         <v>36</v>
       </c>
       <c r="B43" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44">
@@ -1460,7 +1460,7 @@
         <v>37</v>
       </c>
       <c r="B44" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45">
@@ -1476,7 +1476,7 @@
         <v>39</v>
       </c>
       <c r="B46" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47">
@@ -1484,7 +1484,7 @@
         <v>40</v>
       </c>
       <c r="B47" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48">
@@ -1574,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -1582,7 +1582,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -1590,7 +1590,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -1598,7 +1598,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -1606,7 +1606,7 @@
         <v>5</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -1614,7 +1614,7 @@
         <v>6</v>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -1622,7 +1622,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -1630,7 +1630,7 @@
         <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -1638,7 +1638,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1646,7 +1646,7 @@
         <v>10</v>
       </c>
       <c r="B17" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1654,7 +1654,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
@@ -1662,7 +1662,7 @@
         <v>12</v>
       </c>
       <c r="B19" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -1670,7 +1670,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -1678,7 +1678,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -1686,7 +1686,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -1694,7 +1694,7 @@
         <v>16</v>
       </c>
       <c r="B23" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -1702,7 +1702,7 @@
         <v>17</v>
       </c>
       <c r="B24" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25">
@@ -1710,7 +1710,7 @@
         <v>18</v>
       </c>
       <c r="B25" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
@@ -1718,7 +1718,7 @@
         <v>19</v>
       </c>
       <c r="B26" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27">
@@ -1726,7 +1726,7 @@
         <v>20</v>
       </c>
       <c r="B27" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
@@ -1734,7 +1734,7 @@
         <v>21</v>
       </c>
       <c r="B28" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
@@ -1742,7 +1742,7 @@
         <v>22</v>
       </c>
       <c r="B29" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
@@ -1750,7 +1750,7 @@
         <v>23</v>
       </c>
       <c r="B30" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31">
@@ -1758,7 +1758,7 @@
         <v>24</v>
       </c>
       <c r="B31" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32">
@@ -1766,7 +1766,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33">
@@ -1774,7 +1774,7 @@
         <v>26</v>
       </c>
       <c r="B33" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
@@ -1782,7 +1782,7 @@
         <v>27</v>
       </c>
       <c r="B34" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35">
@@ -1790,7 +1790,7 @@
         <v>28</v>
       </c>
       <c r="B35" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36">
@@ -1798,7 +1798,7 @@
         <v>29</v>
       </c>
       <c r="B36" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37">
@@ -1806,7 +1806,7 @@
         <v>30</v>
       </c>
       <c r="B37" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38">
@@ -1814,7 +1814,7 @@
         <v>31</v>
       </c>
       <c r="B38" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39">
@@ -1822,7 +1822,7 @@
         <v>32</v>
       </c>
       <c r="B39" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -1920,7 +1920,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -1928,7 +1928,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -1936,7 +1936,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -1944,7 +1944,7 @@
         <v>5</v>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -1952,7 +1952,7 @@
         <v>6</v>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -1960,7 +1960,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -1976,7 +1976,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
@@ -1984,7 +1984,7 @@
         <v>10</v>
       </c>
       <c r="B17" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
@@ -1992,7 +1992,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -2000,7 +2000,7 @@
         <v>12</v>
       </c>
       <c r="B19" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
@@ -2008,7 +2008,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -2016,7 +2016,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
@@ -2032,7 +2032,7 @@
         <v>16</v>
       </c>
       <c r="B23" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
@@ -2040,7 +2040,7 @@
         <v>17</v>
       </c>
       <c r="B24" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
@@ -2048,7 +2048,7 @@
         <v>18</v>
       </c>
       <c r="B25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
@@ -2056,7 +2056,7 @@
         <v>19</v>
       </c>
       <c r="B26" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
@@ -2064,7 +2064,7 @@
         <v>20</v>
       </c>
       <c r="B27" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
@@ -2072,7 +2072,7 @@
         <v>21</v>
       </c>
       <c r="B28" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -2080,7 +2080,7 @@
         <v>22</v>
       </c>
       <c r="B29" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -2088,7 +2088,7 @@
         <v>23</v>
       </c>
       <c r="B30" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
@@ -2096,7 +2096,7 @@
         <v>24</v>
       </c>
       <c r="B31" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32">
@@ -2104,7 +2104,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33">
@@ -2112,7 +2112,7 @@
         <v>26</v>
       </c>
       <c r="B33" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
@@ -2120,7 +2120,7 @@
         <v>27</v>
       </c>
       <c r="B34" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35">
@@ -2128,7 +2128,7 @@
         <v>28</v>
       </c>
       <c r="B35" t="n">
-        <v>91</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
@@ -2136,7 +2136,7 @@
         <v>29</v>
       </c>
       <c r="B36" t="n">
-        <v>97</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37">
@@ -2144,7 +2144,7 @@
         <v>30</v>
       </c>
       <c r="B37" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38">
@@ -2152,7 +2152,7 @@
         <v>31</v>
       </c>
       <c r="B38" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39">
@@ -2160,7 +2160,7 @@
         <v>32</v>
       </c>
       <c r="B39" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40">
@@ -2168,7 +2168,7 @@
         <v>33</v>
       </c>
       <c r="B40" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
@@ -2176,7 +2176,7 @@
         <v>34</v>
       </c>
       <c r="B41" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42">
@@ -2184,7 +2184,7 @@
         <v>35</v>
       </c>
       <c r="B42" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43">
@@ -2192,7 +2192,7 @@
         <v>36</v>
       </c>
       <c r="B43" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44">
@@ -2200,7 +2200,7 @@
         <v>37</v>
       </c>
       <c r="B44" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45">
@@ -2208,7 +2208,7 @@
         <v>38</v>
       </c>
       <c r="B45" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46">
@@ -2216,7 +2216,7 @@
         <v>39</v>
       </c>
       <c r="B46" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47">
@@ -2224,7 +2224,7 @@
         <v>40</v>
       </c>
       <c r="B47" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48">
@@ -2240,7 +2240,7 @@
         <v>42</v>
       </c>
       <c r="B49" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50">
@@ -2248,7 +2248,7 @@
         <v>43</v>
       </c>
       <c r="B50" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51">
@@ -2256,7 +2256,7 @@
         <v>44</v>
       </c>
       <c r="B51" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52">
@@ -2264,7 +2264,7 @@
         <v>45</v>
       </c>
       <c r="B52" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53">
@@ -2272,7 +2272,7 @@
         <v>46</v>
       </c>
       <c r="B53" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54">
@@ -2280,7 +2280,7 @@
         <v>47</v>
       </c>
       <c r="B54" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55">
@@ -2288,7 +2288,7 @@
         <v>48</v>
       </c>
       <c r="B55" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56">
@@ -2296,7 +2296,7 @@
         <v>49</v>
       </c>
       <c r="B56" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57">
@@ -2304,7 +2304,7 @@
         <v>50</v>
       </c>
       <c r="B57" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58">
@@ -2312,7 +2312,7 @@
         <v>51</v>
       </c>
       <c r="B58" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59">
@@ -2320,7 +2320,7 @@
         <v>52</v>
       </c>
       <c r="B59" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60">
@@ -2328,7 +2328,7 @@
         <v>53</v>
       </c>
       <c r="B60" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61">
@@ -2336,7 +2336,7 @@
         <v>54</v>
       </c>
       <c r="B61" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62">
@@ -2344,7 +2344,7 @@
         <v>55</v>
       </c>
       <c r="B62" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63">
@@ -2352,7 +2352,7 @@
         <v>56</v>
       </c>
       <c r="B63" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64">
@@ -2360,7 +2360,7 @@
         <v>57</v>
       </c>
       <c r="B64" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65">
@@ -2368,7 +2368,7 @@
         <v>58</v>
       </c>
       <c r="B65" t="n">
-        <v>67</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66">
@@ -2376,7 +2376,7 @@
         <v>59</v>
       </c>
       <c r="B66" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67">
@@ -2384,7 +2384,7 @@
         <v>60</v>
       </c>
       <c r="B67" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68">
@@ -2392,7 +2392,7 @@
         <v>61</v>
       </c>
       <c r="B68" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69">
@@ -2400,7 +2400,7 @@
         <v>62</v>
       </c>
       <c r="B69" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70">
@@ -2408,7 +2408,7 @@
         <v>63</v>
       </c>
       <c r="B70" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71">
@@ -2416,7 +2416,7 @@
         <v>64</v>
       </c>
       <c r="B71" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72">
@@ -2424,7 +2424,7 @@
         <v>65</v>
       </c>
       <c r="B72" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73">
@@ -2432,7 +2432,7 @@
         <v>66</v>
       </c>
       <c r="B73" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74">
@@ -2440,7 +2440,7 @@
         <v>67</v>
       </c>
       <c r="B74" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75">
@@ -2448,7 +2448,7 @@
         <v>68</v>
       </c>
       <c r="B75" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76">
@@ -2456,7 +2456,7 @@
         <v>69</v>
       </c>
       <c r="B76" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77">
@@ -2464,7 +2464,7 @@
         <v>70</v>
       </c>
       <c r="B77" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
     </row>
     <row r="78">
@@ -2472,7 +2472,7 @@
         <v>71</v>
       </c>
       <c r="B78" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
     </row>
     <row r="79">
@@ -2480,7 +2480,7 @@
         <v>72</v>
       </c>
       <c r="B79" t="n">
-        <v>33</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80">
@@ -2488,7 +2488,7 @@
         <v>73</v>
       </c>
       <c r="B80" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81">
@@ -2496,7 +2496,7 @@
         <v>74</v>
       </c>
       <c r="B81" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82">
@@ -2504,7 +2504,7 @@
         <v>75</v>
       </c>
       <c r="B82" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83">
@@ -2512,7 +2512,7 @@
         <v>76</v>
       </c>
       <c r="B83" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84">
@@ -2520,7 +2520,7 @@
         <v>77</v>
       </c>
       <c r="B84" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85">
@@ -2528,7 +2528,7 @@
         <v>78</v>
       </c>
       <c r="B85" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86">
@@ -2536,7 +2536,7 @@
         <v>79</v>
       </c>
       <c r="B86" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87">
@@ -2544,7 +2544,7 @@
         <v>80</v>
       </c>
       <c r="B87" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88">
@@ -2634,7 +2634,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -2642,7 +2642,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -2650,7 +2650,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -2658,7 +2658,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -2674,7 +2674,7 @@
         <v>6</v>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -2682,7 +2682,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -2690,7 +2690,7 @@
         <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -2698,7 +2698,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17">
@@ -2706,7 +2706,7 @@
         <v>10</v>
       </c>
       <c r="B17" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -2714,7 +2714,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -2722,7 +2722,7 @@
         <v>12</v>
       </c>
       <c r="B19" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -2730,7 +2730,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="n">
-        <v>65</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21">
@@ -2738,7 +2738,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="n">
-        <v>54</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
@@ -2746,7 +2746,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23">
@@ -2754,7 +2754,7 @@
         <v>16</v>
       </c>
       <c r="B23" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24">
@@ -2762,7 +2762,7 @@
         <v>17</v>
       </c>
       <c r="B24" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
@@ -2770,7 +2770,7 @@
         <v>18</v>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
@@ -2778,7 +2778,7 @@
         <v>19</v>
       </c>
       <c r="B26" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
@@ -2786,7 +2786,7 @@
         <v>20</v>
       </c>
       <c r="B27" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
@@ -2794,7 +2794,7 @@
         <v>21</v>
       </c>
       <c r="B28" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29">
@@ -2802,7 +2802,7 @@
         <v>22</v>
       </c>
       <c r="B29" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30">
@@ -2810,7 +2810,7 @@
         <v>23</v>
       </c>
       <c r="B30" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31">
@@ -2818,7 +2818,7 @@
         <v>24</v>
       </c>
       <c r="B31" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32">
@@ -2826,7 +2826,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
@@ -2834,7 +2834,7 @@
         <v>26</v>
       </c>
       <c r="B33" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34">
@@ -2842,7 +2842,7 @@
         <v>27</v>
       </c>
       <c r="B34" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35">
@@ -2850,7 +2850,7 @@
         <v>28</v>
       </c>
       <c r="B35" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36">
@@ -2858,7 +2858,7 @@
         <v>29</v>
       </c>
       <c r="B36" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
@@ -2866,7 +2866,7 @@
         <v>30</v>
       </c>
       <c r="B37" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -2874,7 +2874,7 @@
         <v>31</v>
       </c>
       <c r="B38" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -2882,7 +2882,7 @@
         <v>32</v>
       </c>
       <c r="B39" t="n">
-        <v>76</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
@@ -2890,7 +2890,7 @@
         <v>33</v>
       </c>
       <c r="B40" t="n">
-        <v>64</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
@@ -2898,7 +2898,7 @@
         <v>34</v>
       </c>
       <c r="B41" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
@@ -2906,7 +2906,7 @@
         <v>35</v>
       </c>
       <c r="B42" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
@@ -2914,7 +2914,7 @@
         <v>36</v>
       </c>
       <c r="B43" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -2922,7 +2922,7 @@
         <v>37</v>
       </c>
       <c r="B44" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45">
@@ -2930,7 +2930,7 @@
         <v>38</v>
       </c>
       <c r="B45" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46">
@@ -2938,7 +2938,7 @@
         <v>39</v>
       </c>
       <c r="B46" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
@@ -2946,7 +2946,7 @@
         <v>40</v>
       </c>
       <c r="B47" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
@@ -2954,7 +2954,7 @@
         <v>41</v>
       </c>
       <c r="B48" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -2962,7 +2962,7 @@
         <v>42</v>
       </c>
       <c r="B49" t="n">
-        <v>76</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
@@ -2970,7 +2970,7 @@
         <v>43</v>
       </c>
       <c r="B50" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
@@ -2978,7 +2978,7 @@
         <v>44</v>
       </c>
       <c r="B51" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -2986,7 +2986,7 @@
         <v>45</v>
       </c>
       <c r="B52" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
@@ -2994,7 +2994,7 @@
         <v>46</v>
       </c>
       <c r="B53" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54">
@@ -3002,7 +3002,7 @@
         <v>47</v>
       </c>
       <c r="B54" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
@@ -3010,7 +3010,7 @@
         <v>48</v>
       </c>
       <c r="B55" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56">

--- a/examples/data/example_2_one_sheet_per_trial.xlsx
+++ b/examples/data/example_2_one_sheet_per_trial.xlsx
@@ -1120,6 +1120,10 @@
   </sheetPr>
   <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1522,6 +1526,10 @@
   </sheetPr>
   <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1860,6 +1868,10 @@
   </sheetPr>
   <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2582,6 +2594,10 @@
   </sheetPr>
   <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/examples/data/example_2_one_sheet_per_trial.xlsx
+++ b/examples/data/example_2_one_sheet_per_trial.xlsx
@@ -463,6 +463,28 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Site:</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Example farm</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Cultivar:</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Cultivar X</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="B3" s="1" t="inlineStr">
         <is>

--- a/examples/data/example_2_one_sheet_per_trial.xlsx
+++ b/examples/data/example_2_one_sheet_per_trial.xlsx
@@ -455,6 +455,34 @@
   </sheetPr>
   <dimension ref="B1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="5" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
@@ -507,7 +535,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="39.375" customHeight="1">
       <c r="B4" s="2" t="n">
         <v>40</v>
       </c>
@@ -584,7 +612,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="39.375" customHeight="1">
       <c r="B5" s="2" t="n">
         <v>31</v>
       </c>
@@ -661,7 +689,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="39.375" customHeight="1">
       <c r="B6" s="2" t="n">
         <v>30</v>
       </c>
@@ -738,7 +766,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="39.375" customHeight="1">
       <c r="B7" s="2" t="n">
         <v>21</v>
       </c>
@@ -815,7 +843,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="39.375" customHeight="1">
       <c r="B8" s="2" t="n">
         <v>20</v>
       </c>
@@ -892,7 +920,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="39.375" customHeight="1">
       <c r="B9" s="2" t="n">
         <v>11</v>
       </c>
@@ -969,7 +997,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="39.375" customHeight="1">
       <c r="B10" s="2" t="n">
         <v>10</v>
       </c>
@@ -1046,7 +1074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="39.375" customHeight="1">
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>

--- a/examples/data/example_2_one_sheet_per_trial.xlsx
+++ b/examples/data/example_2_one_sheet_per_trial.xlsx
@@ -535,7 +535,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="39.375" customHeight="1">
+    <row r="4" ht="37.5" customHeight="1">
       <c r="B4" s="2" t="n">
         <v>40</v>
       </c>
@@ -612,7 +612,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" ht="39.375" customHeight="1">
+    <row r="5" ht="37.5" customHeight="1">
       <c r="B5" s="2" t="n">
         <v>31</v>
       </c>
@@ -689,7 +689,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" ht="39.375" customHeight="1">
+    <row r="6" ht="37.5" customHeight="1">
       <c r="B6" s="2" t="n">
         <v>30</v>
       </c>
@@ -766,7 +766,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" ht="39.375" customHeight="1">
+    <row r="7" ht="37.5" customHeight="1">
       <c r="B7" s="2" t="n">
         <v>21</v>
       </c>
@@ -843,7 +843,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" ht="39.375" customHeight="1">
+    <row r="8" ht="37.5" customHeight="1">
       <c r="B8" s="2" t="n">
         <v>20</v>
       </c>
@@ -920,7 +920,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" ht="39.375" customHeight="1">
+    <row r="9" ht="37.5" customHeight="1">
       <c r="B9" s="2" t="n">
         <v>11</v>
       </c>
@@ -997,7 +997,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="39.375" customHeight="1">
+    <row r="10" ht="37.5" customHeight="1">
       <c r="B10" s="2" t="n">
         <v>10</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" ht="39.375" customHeight="1">
+    <row r="11" ht="37.5" customHeight="1">
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
